--- a/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
+++ b/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="143">
   <si>
     <t>Tarea</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Riesgos 24/10</t>
+  </si>
+  <si>
+    <t>1:27:40</t>
   </si>
   <si>
     <t>Identificación y evaluación de riesgos</t>
@@ -2011,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E29" s="14">
         <v>45954.0</v>
@@ -2021,7 +2024,9 @@
       </c>
       <c r="G29" s="44"/>
       <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
+      <c r="I29" s="42" t="s">
+        <v>79</v>
+      </c>
       <c r="J29" s="43"/>
     </row>
   </sheetData>
@@ -2122,7 +2127,7 @@
     </row>
     <row r="2">
       <c r="A2" s="46" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -2140,16 +2145,16 @@
         <v>45923.0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="46" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>17</v>
@@ -2167,22 +2172,22 @@
         <v>45924.0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
@@ -2194,16 +2199,16 @@
         <v>45924.0</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>11</v>
@@ -2221,16 +2226,16 @@
         <v>45926.0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>11</v>
@@ -2248,22 +2253,22 @@
         <v>45926.0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>13</v>
@@ -2275,16 +2280,16 @@
         <v>45927.0</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>33</v>
@@ -2302,16 +2307,16 @@
         <v>45926.0</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>17</v>
@@ -2329,16 +2334,16 @@
         <v>45928.0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>17</v>
@@ -2356,7 +2361,7 @@
         <v>45929.0</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="9" t="s">
@@ -2369,7 +2374,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>17</v>
@@ -2387,16 +2392,16 @@
         <v>45930.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>33</v>
@@ -2412,16 +2417,16 @@
         <v>45930.0</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>64</v>
@@ -2437,16 +2442,16 @@
         <v>45926.0</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>21</v>
@@ -2464,16 +2469,16 @@
         <v>45929.0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -2491,16 +2496,16 @@
         <v>45930.0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>21</v>
@@ -2518,7 +2523,7 @@
         <v>45930.0</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" s="33"/>
       <c r="I16" s="34" t="s">
@@ -2527,14 +2532,14 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="7">
         <v>45930.0</v>
@@ -2543,16 +2548,16 @@
         <v>45930.0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>64</v>
@@ -2568,19 +2573,19 @@
         <v>45901.0</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
@@ -2595,7 +2600,7 @@
         <v>45931.0</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="9" t="s">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>30</v>
@@ -2622,16 +2627,16 @@
         <v>45934.0</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>64</v>
@@ -2649,16 +2654,16 @@
         <v>45933.0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>21</v>
@@ -2676,19 +2681,19 @@
         <v>45933.0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="5" t="s">
@@ -2701,14 +2706,14 @@
         <v>45932.0</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="54"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>33</v>
@@ -2726,16 +2731,16 @@
         <v>45937.0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>21</v>
@@ -2753,19 +2758,19 @@
         <v>45936.0</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
@@ -2778,14 +2783,14 @@
         <v>45934.0</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="54"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>33</v>
@@ -2801,14 +2806,14 @@
         <v>45934.0</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="54"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>51</v>
@@ -2826,16 +2831,16 @@
         <v>45935.0</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>51</v>
@@ -2853,16 +2858,16 @@
         <v>45935.0</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H29" s="24"/>
       <c r="I29" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="60" t="s">
         <v>51</v>
@@ -2880,16 +2885,16 @@
         <v>45936.0</v>
       </c>
       <c r="G30" s="64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H30" s="65"/>
       <c r="I30" s="66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
@@ -2909,12 +2914,12 @@
       <c r="G31" s="4"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
@@ -2932,16 +2937,16 @@
         <v>45940.0</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
@@ -2959,16 +2964,16 @@
         <v>45940.0</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
@@ -2986,16 +2991,16 @@
         <v>45933.0</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>33</v>
@@ -3015,12 +3020,12 @@
       <c r="G35" s="4"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>33</v>
@@ -3036,11 +3041,11 @@
         <v>46301.0</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H36" s="8"/>
       <c r="I36" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37">
@@ -3205,7 +3210,7 @@
     </row>
     <row r="43">
       <c r="A43" s="67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B43" s="68" t="s">
         <v>51</v>
@@ -3225,7 +3230,7 @@
       <c r="G43" s="71"/>
       <c r="H43" s="71"/>
       <c r="I43" s="72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44">

--- a/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
+++ b/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="150">
   <si>
     <t>Tarea</t>
   </si>
@@ -254,6 +254,27 @@
   </si>
   <si>
     <t>1:27:40</t>
+  </si>
+  <si>
+    <t>Caso de prueba 12 estimar tarea</t>
+  </si>
+  <si>
+    <t>28/10/25</t>
+  </si>
+  <si>
+    <t>00:10:05</t>
+  </si>
+  <si>
+    <t>CU20: Registrar tiempo por cronometro</t>
+  </si>
+  <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>05:24:00</t>
+  </si>
+  <si>
+    <t>06:13:00</t>
   </si>
   <si>
     <t>Identificación y evaluación de riesgos</t>
@@ -1008,7 +1029,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J29" displayName="Tabla_1" name="Tabla_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J33" displayName="Tabla_1" name="Tabla_1" id="1">
   <tableColumns count="10">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -2029,18 +2050,122 @@
       </c>
       <c r="J29" s="43"/>
     </row>
+    <row r="30">
+      <c r="A30" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="14">
+        <v>45955.0</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="43"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="14">
+        <v>45954.0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>45954.0</v>
+      </c>
+      <c r="G31" s="44"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="43"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="14">
+        <v>45955.0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>45955.0</v>
+      </c>
+      <c r="G32" s="44"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="J32" s="43"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="14">
+        <v>45956.0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>45956.0</v>
+      </c>
+      <c r="G33" s="44"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="43"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D29">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D33">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B29">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B33">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:F29">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:F33">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A29 G2:G29 I2:I29"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A33 G2:G33 I2:I33"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C2"/>
@@ -2070,10 +2195,14 @@
     <hyperlink r:id="rId25" ref="C27"/>
     <hyperlink r:id="rId26" ref="C28"/>
     <hyperlink r:id="rId27" ref="C29"/>
+    <hyperlink r:id="rId28" ref="C30"/>
+    <hyperlink r:id="rId29" ref="C31"/>
+    <hyperlink r:id="rId30" ref="C32"/>
+    <hyperlink r:id="rId31" ref="C33"/>
   </hyperlinks>
-  <drawing r:id="rId28"/>
+  <drawing r:id="rId32"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId34"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2127,7 +2256,7 @@
     </row>
     <row r="2">
       <c r="A2" s="46" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -2145,16 +2274,16 @@
         <v>45923.0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="46" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>17</v>
@@ -2172,22 +2301,22 @@
         <v>45924.0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="46" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
@@ -2199,16 +2328,16 @@
         <v>45924.0</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>11</v>
@@ -2226,16 +2355,16 @@
         <v>45926.0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>11</v>
@@ -2253,22 +2382,22 @@
         <v>45926.0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="46" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>13</v>
@@ -2280,16 +2409,16 @@
         <v>45927.0</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>33</v>
@@ -2307,16 +2436,16 @@
         <v>45926.0</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>17</v>
@@ -2334,16 +2463,16 @@
         <v>45928.0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>17</v>
@@ -2361,7 +2490,7 @@
         <v>45929.0</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="9" t="s">
@@ -2374,7 +2503,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>17</v>
@@ -2392,16 +2521,16 @@
         <v>45930.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="9" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>33</v>
@@ -2417,16 +2546,16 @@
         <v>45930.0</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>64</v>
@@ -2442,16 +2571,16 @@
         <v>45926.0</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>21</v>
@@ -2469,16 +2598,16 @@
         <v>45929.0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -2496,16 +2625,16 @@
         <v>45930.0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="50" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>21</v>
@@ -2523,7 +2652,7 @@
         <v>45930.0</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H16" s="33"/>
       <c r="I16" s="34" t="s">
@@ -2532,14 +2661,14 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E17" s="7">
         <v>45930.0</v>
@@ -2548,16 +2677,16 @@
         <v>45930.0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>64</v>
@@ -2573,19 +2702,19 @@
         <v>45901.0</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
@@ -2600,7 +2729,7 @@
         <v>45931.0</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="9" t="s">
@@ -2609,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>30</v>
@@ -2627,16 +2756,16 @@
         <v>45934.0</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>64</v>
@@ -2654,16 +2783,16 @@
         <v>45933.0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>21</v>
@@ -2681,19 +2810,19 @@
         <v>45933.0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="9" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="5" t="s">
@@ -2706,14 +2835,14 @@
         <v>45932.0</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="54"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>33</v>
@@ -2731,16 +2860,16 @@
         <v>45937.0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>21</v>
@@ -2758,19 +2887,19 @@
         <v>45936.0</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
@@ -2783,14 +2912,14 @@
         <v>45934.0</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="54"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>33</v>
@@ -2806,14 +2935,14 @@
         <v>45934.0</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="54"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>51</v>
@@ -2831,16 +2960,16 @@
         <v>45935.0</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>51</v>
@@ -2858,16 +2987,16 @@
         <v>45935.0</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H29" s="24"/>
       <c r="I29" s="25" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="55" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B30" s="60" t="s">
         <v>51</v>
@@ -2885,16 +3014,16 @@
         <v>45936.0</v>
       </c>
       <c r="G30" s="64" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H30" s="65"/>
       <c r="I30" s="66" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
@@ -2914,12 +3043,12 @@
       <c r="G31" s="4"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
@@ -2937,16 +3066,16 @@
         <v>45940.0</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
@@ -2964,16 +3093,16 @@
         <v>45940.0</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="9" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
@@ -2991,16 +3120,16 @@
         <v>45933.0</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="9" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>33</v>
@@ -3020,12 +3149,12 @@
       <c r="G35" s="4"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>33</v>
@@ -3041,11 +3170,11 @@
         <v>46301.0</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H36" s="8"/>
       <c r="I36" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37">
@@ -3210,7 +3339,7 @@
     </row>
     <row r="43">
       <c r="A43" s="67" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B43" s="68" t="s">
         <v>51</v>
@@ -3230,7 +3359,7 @@
       <c r="G43" s="71"/>
       <c r="H43" s="71"/>
       <c r="I43" s="72" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">

--- a/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
+++ b/Registro de tiempos por tarea - Kairos _ NexTech.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="219">
   <si>
     <t>Fase Construcción Iteración 2</t>
   </si>
@@ -32,16 +32,16 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>Fecha de inicio (estimada)</t>
-  </si>
-  <si>
-    <t>Fecha de finalización (estimada)</t>
-  </si>
-  <si>
-    <t>Fecha de inicio real</t>
-  </si>
-  <si>
-    <t>Fecha de finalización real</t>
+    <t>Fecha inicio plan</t>
+  </si>
+  <si>
+    <t>Fecha fin plan</t>
+  </si>
+  <si>
+    <t>Fecha inicio real</t>
+  </si>
+  <si>
+    <t>Fecha fin real</t>
   </si>
   <si>
     <t>Fecha de Entrega</t>
@@ -65,193 +65,202 @@
     <t>Completado</t>
   </si>
   <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>00:23:56</t>
+  </si>
+  <si>
+    <t>Revisión documento priorizacion CU2</t>
+  </si>
+  <si>
+    <t>Validación y Verificación</t>
+  </si>
+  <si>
+    <t>Agustina Maldonado</t>
+  </si>
+  <si>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>00:05:00</t>
+  </si>
+  <si>
+    <t>Ajustar documentos en la rama main</t>
+  </si>
+  <si>
+    <t>Actividades Externas</t>
+  </si>
+  <si>
+    <t>Sin comenzar</t>
+  </si>
+  <si>
+    <t>Especificación de CU13: Asignar dependencia / CU14: Modificar estado de tarea</t>
+  </si>
+  <si>
+    <t>Diseño</t>
+  </si>
+  <si>
+    <t>4/11/2025</t>
+  </si>
+  <si>
+    <t>01:43:00</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU13 y CU14</t>
+  </si>
+  <si>
+    <t>Florencia Mendez</t>
+  </si>
+  <si>
+    <t>Especificación de CU15: Visualizar Tarea / CU16: Comentar Tarea</t>
+  </si>
+  <si>
+    <t>esstefaniamendez@gmail.com</t>
+  </si>
+  <si>
+    <t>03:44:13</t>
+  </si>
+  <si>
+    <t>Revisión de CU13 y CU14</t>
+  </si>
+  <si>
+    <t>Especificación de CU07: Crear Etapa</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU07 crear etapa</t>
+  </si>
+  <si>
+    <t>Especificación de CU08: Crear Iteración</t>
+  </si>
+  <si>
+    <t>0:34:21</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU08 crear etapa</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU15 y CU16</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>Especificación de CU21: Registrar tiempo manual</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU21</t>
+  </si>
+  <si>
+    <t>guilleh114@gmail.com</t>
+  </si>
+  <si>
+    <t>Implementación CU13 Asignar dependencia</t>
+  </si>
+  <si>
+    <t>Codificación</t>
+  </si>
+  <si>
+    <t>Implementación CU14 Modificar estado tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU15 visualizar tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU16 comentar tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU21 registrar tiempo manual</t>
+  </si>
+  <si>
+    <t>gonzalo.ulloa99@gmail.com</t>
+  </si>
+  <si>
+    <t>Implementación CU07 crear etapa</t>
+  </si>
+  <si>
+    <t>centurionvaleria6@gmail.com</t>
+  </si>
+  <si>
+    <t>4:30:00</t>
+  </si>
+  <si>
+    <t>no planificado</t>
+  </si>
+  <si>
+    <t>Implemntación CU08 crear iteracion</t>
+  </si>
+  <si>
+    <t>5:25:00</t>
+  </si>
+  <si>
+    <t>Definición casos de prueba para CU Gestionar tareas</t>
+  </si>
+  <si>
+    <t>Análisis</t>
+  </si>
+  <si>
+    <t>Definición casos de prueba para los CU07 Crear etapa, CU08 Crear iteración</t>
+  </si>
+  <si>
+    <t>Definición casos de prueba para los CU21 Registrar tiempo manual</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU13: Asignar dependencia / CU14: Modificar estado de tarea</t>
+  </si>
+  <si>
+    <t>Revisión Casos de Prueba CU13, CU14</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU15: Visualizar Tarea / CU16: Comentar Tarea</t>
+  </si>
+  <si>
+    <t>Revisión Casos de Prueba CU15, CU16</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU21: Registrar tiempo manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agustina Maldonado </t>
+  </si>
+  <si>
+    <t>Revisión Caso de Prueba CU21</t>
+  </si>
+  <si>
+    <t>Cierre Fase Construcción Iteración 2</t>
+  </si>
+  <si>
+    <t>Revisión Cierre de Fase</t>
+  </si>
+  <si>
+    <t>Plan de Iteración 3 Fase Construcción con Estimación y Gestión de Riesgos</t>
+  </si>
+  <si>
+    <t>Revisión Plan de Iteración</t>
+  </si>
+  <si>
+    <t>Fase Construcción Iteración 1</t>
+  </si>
+  <si>
+    <t>Fecha de inicio</t>
+  </si>
+  <si>
+    <t>Fecha de finalización</t>
+  </si>
+  <si>
+    <t>Producto final</t>
+  </si>
+  <si>
+    <t>Columna 1</t>
+  </si>
+  <si>
+    <t>Modelo Arquitectónico</t>
+  </si>
+  <si>
     <t>14/10/25</t>
-  </si>
-  <si>
-    <t>00:23:56</t>
-  </si>
-  <si>
-    <t>Revisión documento priorizacion CU2</t>
-  </si>
-  <si>
-    <t>Validación y Verificación</t>
-  </si>
-  <si>
-    <t>Agustina Maldonado</t>
-  </si>
-  <si>
-    <t>00:05:00</t>
-  </si>
-  <si>
-    <t>Ajustar documentos en la rama main</t>
-  </si>
-  <si>
-    <t>Actividades Externas</t>
-  </si>
-  <si>
-    <t>Sin comenzar</t>
-  </si>
-  <si>
-    <t>Especificación de CU13: Asignar dependencia / CU14: Modificar estado de tarea</t>
-  </si>
-  <si>
-    <t>Diseño</t>
-  </si>
-  <si>
-    <t>En curso</t>
-  </si>
-  <si>
-    <t>4/11/2025</t>
-  </si>
-  <si>
-    <t>00:26:58</t>
-  </si>
-  <si>
-    <t>Revisión Especificación CU13 y CU14</t>
-  </si>
-  <si>
-    <t>Florencia Mendez</t>
-  </si>
-  <si>
-    <t>Especificación de CU15: Visualizar Tarea / CU16: Comentar Tarea</t>
-  </si>
-  <si>
-    <t>esstefaniamendez@gmail.com</t>
-  </si>
-  <si>
-    <t>03:03:44</t>
-  </si>
-  <si>
-    <t>Revisión de CU13 y CU14</t>
-  </si>
-  <si>
-    <t>Especificación de CU07: Crear Etapa</t>
-  </si>
-  <si>
-    <t>Revisión Especificación CU07 crear etapa</t>
-  </si>
-  <si>
-    <t>Especificación de CU08: Crear Iteración</t>
-  </si>
-  <si>
-    <t>Revisión Especificación CU08 crear etapa</t>
-  </si>
-  <si>
-    <t>Revisión Especificación CU15 y CU16</t>
-  </si>
-  <si>
-    <t>14/10/2025</t>
-  </si>
-  <si>
-    <t>Especificación de CU21: Registrar tiempo manual</t>
-  </si>
-  <si>
-    <t>Revisión Especificación CU21</t>
-  </si>
-  <si>
-    <t>guilleh114@gmail.com</t>
-  </si>
-  <si>
-    <t>Implementación CU13 Asignar dependencia</t>
-  </si>
-  <si>
-    <t>Codificación</t>
-  </si>
-  <si>
-    <t>Implementación CU14 Modificar estado tarea</t>
-  </si>
-  <si>
-    <t>Implementación CU15 visualizar tarea</t>
-  </si>
-  <si>
-    <t>Implementación CU16 comentar tarea</t>
-  </si>
-  <si>
-    <t>Implementación CU21 registrar tiempo manual</t>
-  </si>
-  <si>
-    <t>gonzalo.ulloa99@gmail.com</t>
-  </si>
-  <si>
-    <t>Implementación CU07 crear etapa</t>
-  </si>
-  <si>
-    <t>centurionvaleria6@gmail.com</t>
-  </si>
-  <si>
-    <t>2:30:00</t>
-  </si>
-  <si>
-    <t>no planificado</t>
-  </si>
-  <si>
-    <t>Implemntación CU08 crear iteracion</t>
-  </si>
-  <si>
-    <t>4:25:00</t>
-  </si>
-  <si>
-    <t>Definición casos de prueba para CU Gestionar tareas</t>
-  </si>
-  <si>
-    <t>Análisis</t>
-  </si>
-  <si>
-    <t>Definición casos de prueba para los CU07 Crear etapa, CU08 Crear iteración</t>
-  </si>
-  <si>
-    <t>Definición casos de prueba para los CU21 Registrar tiempo manual</t>
-  </si>
-  <si>
-    <t>Ejecución de Casos de prueba de CU13: Asignar dependencia / CU14: Modificar estado de tarea</t>
-  </si>
-  <si>
-    <t>Revisión Casos de Prueba CU13, CU14</t>
-  </si>
-  <si>
-    <t>Ejecución de Casos de prueba de CU15: Visualizar Tarea / CU16: Comentar Tarea</t>
-  </si>
-  <si>
-    <t>Revisión Casos de Prueba CU15, CU16</t>
-  </si>
-  <si>
-    <t>Ejecución de Casos de prueba de CU21: Registrar tiempo manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agustina Maldonado </t>
-  </si>
-  <si>
-    <t>Revisión Caso de Prueba CU21</t>
-  </si>
-  <si>
-    <t>Cierre Fase Construcción Iteración 2</t>
-  </si>
-  <si>
-    <t>Revisión Cierre de Fase</t>
-  </si>
-  <si>
-    <t>Plan de Iteración 3 Fase Construcción con Estimación y Gestión de Riesgos</t>
-  </si>
-  <si>
-    <t>Revisión Plan de Iteración</t>
-  </si>
-  <si>
-    <t>Fase Construcción Iteración 1</t>
-  </si>
-  <si>
-    <t>Fecha de inicio</t>
-  </si>
-  <si>
-    <t>Fecha de finalización</t>
-  </si>
-  <si>
-    <t>Producto final</t>
-  </si>
-  <si>
-    <t>Columna 1</t>
-  </si>
-  <si>
-    <t>Modelo Arquitectónico</t>
   </si>
   <si>
     <t>4:35:00</t>
@@ -855,7 +864,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -883,20 +892,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9DAF8"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC9DAF8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9DAF8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC9DAF8"/>
       </bottom>
     </border>
     <border>
@@ -1101,6 +1096,9 @@
     <xf borderId="0" fillId="7" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="7" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1113,16 +1111,13 @@
     <xf borderId="2" fillId="8" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="5" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="8" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1170,7 +1165,7 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="8" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="8" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1191,7 +1186,7 @@
     <xf borderId="2" fillId="8" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="8" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="6" fillId="8" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1203,22 +1198,22 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="9" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="9" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="9" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="9" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="8" fillId="9" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1282,22 +1277,22 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="10" fillId="9" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="9" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="9" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="9" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="8" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="8" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="8" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1333,22 +1328,22 @@
     <xf borderId="0" fillId="8" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="8" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="8" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="23" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="8" fontId="23" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="8" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="24" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="8" fontId="24" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="13" fillId="8" fontId="22" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="12" fillId="8" fontId="22" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1465,10 +1460,10 @@
     <tableColumn name="Categoría" id="2"/>
     <tableColumn name="Propietario" id="3"/>
     <tableColumn name="Estado" id="4"/>
-    <tableColumn name="Fecha de inicio (estimada)" id="5"/>
-    <tableColumn name="Fecha de finalización (estimada)" id="6"/>
-    <tableColumn name="Fecha de inicio real" id="7"/>
-    <tableColumn name="Fecha de finalización real" id="8"/>
+    <tableColumn name="Fecha inicio plan" id="5"/>
+    <tableColumn name="Fecha fin plan" id="6"/>
+    <tableColumn name="Fecha inicio real" id="7"/>
+    <tableColumn name="Fecha fin real" id="8"/>
     <tableColumn name="Fecha de Entrega" id="9"/>
     <tableColumn name="Tiempo registrado" id="10"/>
     <tableColumn name="Notas" id="11"/>
@@ -1718,10 +1713,11 @@
     <col customWidth="1" min="2" max="2" width="18.25"/>
     <col customWidth="1" min="3" max="3" width="17.25"/>
     <col customWidth="1" min="4" max="4" width="15.25"/>
-    <col customWidth="1" min="5" max="5" width="18.88"/>
-    <col customWidth="1" min="6" max="6" width="18.13"/>
-    <col customWidth="1" min="7" max="7" width="15.88"/>
-    <col customWidth="1" min="8" max="9" width="16.5"/>
+    <col customWidth="1" min="5" max="5" width="16.13"/>
+    <col customWidth="1" min="6" max="6" width="13.63"/>
+    <col customWidth="1" min="7" max="7" width="14.63"/>
+    <col customWidth="1" min="8" max="8" width="12.75"/>
+    <col customWidth="1" min="9" max="9" width="16.5"/>
     <col customWidth="1" min="10" max="10" width="15.0"/>
   </cols>
   <sheetData>
@@ -1823,24 +1819,26 @@
       <c r="H5" s="17">
         <v>45960.0</v>
       </c>
-      <c r="I5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="J5" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" s="13"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="8">
         <v>45961.0</v>
@@ -1856,16 +1854,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E7" s="15">
         <v>45963.0</v>
@@ -1876,7 +1874,9 @@
       <c r="G7" s="17">
         <v>45964.0</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="17">
+        <v>45965.0</v>
+      </c>
       <c r="I7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="8">
         <v>45965.0</v>
@@ -1917,13 +1917,13 @@
         <v>32</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E9" s="15">
         <v>45963.0</v>
@@ -1934,7 +1934,9 @@
       <c r="G9" s="18">
         <v>45960.0</v>
       </c>
-      <c r="H9" s="17"/>
+      <c r="H9" s="17">
+        <v>45965.0</v>
+      </c>
       <c r="I9" s="11" t="s">
         <v>28</v>
       </c>
@@ -1954,12 +1956,16 @@
         <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="E10" s="8">
+        <v>45965.0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>45965.0</v>
+      </c>
       <c r="G10" s="19"/>
-      <c r="H10" s="17"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="11"/>
       <c r="J10" s="12"/>
       <c r="K10" s="13"/>
@@ -1969,17 +1975,21 @@
         <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="E11" s="15">
+        <v>45963.0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>45965.0</v>
+      </c>
+      <c r="G11" s="20"/>
       <c r="H11" s="17"/>
       <c r="I11" s="11"/>
       <c r="J11" s="12"/>
@@ -1987,7 +1997,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>19</v>
@@ -1996,52 +2006,72 @@
         <v>33</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>45965.0</v>
+      </c>
+      <c r="F12" s="8">
+        <v>45965.0</v>
+      </c>
       <c r="G12" s="19"/>
-      <c r="H12" s="17"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="11"/>
       <c r="J12" s="12"/>
       <c r="K12" s="13"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="E13" s="15">
+        <v>45963.0</v>
+      </c>
+      <c r="F13" s="15">
+        <v>45965.0</v>
+      </c>
+      <c r="G13" s="20">
+        <v>45964.0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>45965.0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K13" s="13"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="21" t="s">
+      <c r="A14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="D14" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="8">
+        <v>45965.0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>45965.0</v>
+      </c>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="25"/>
@@ -2063,7 +2093,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>19</v>
@@ -2072,244 +2102,248 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="8">
+        <v>25</v>
+      </c>
+      <c r="E15" s="15">
         <v>45965.0</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="15">
         <v>45965.0</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="13"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="15">
+        <v>25</v>
+      </c>
+      <c r="E16" s="8">
         <v>45963.0</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="8">
         <v>45965.0</v>
       </c>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="11"/>
       <c r="J16" s="12"/>
       <c r="K16" s="13"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8">
+        <v>25</v>
+      </c>
+      <c r="E17" s="15">
         <v>45965.0</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="15">
         <v>45965.0</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="29"/>
       <c r="J17" s="12"/>
       <c r="K17" s="13"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="29"/>
       <c r="J18" s="12"/>
       <c r="K18" s="13"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="29"/>
       <c r="J19" s="12"/>
       <c r="K19" s="13"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="29"/>
       <c r="J20" s="12"/>
       <c r="K20" s="13"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="29"/>
       <c r="J21" s="12"/>
       <c r="K21" s="13"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="29"/>
       <c r="J22" s="12"/>
       <c r="K22" s="13"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="8">
+        <v>37</v>
+      </c>
+      <c r="E23" s="15">
         <v>45959.0</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="29"/>
       <c r="J23" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K23" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="15">
+        <v>37</v>
+      </c>
+      <c r="E24" s="8">
         <v>45963.0</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="29"/>
       <c r="J24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="K24" s="30" t="s">
         <v>57</v>
-      </c>
-      <c r="K24" s="30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="E25" s="15">
+        <v>45965.0</v>
+      </c>
+      <c r="F25" s="15">
+        <v>45967.0</v>
+      </c>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
       <c r="I25" s="29"/>
@@ -2318,36 +2352,44 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" s="32"/>
       <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+        <v>25</v>
+      </c>
+      <c r="E26" s="8">
+        <v>45965.0</v>
+      </c>
+      <c r="F26" s="8">
+        <v>45967.0</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="29"/>
       <c r="J26" s="12"/>
       <c r="K26" s="30"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="C27" s="32"/>
       <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="E27" s="15">
+        <v>45965.0</v>
+      </c>
+      <c r="F27" s="15">
+        <v>45967.0</v>
+      </c>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="29"/>
@@ -2356,7 +2398,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>19</v>
@@ -2365,7 +2407,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" s="8">
         <v>45965.0</v>
@@ -2381,7 +2423,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>19</v>
@@ -2390,7 +2432,7 @@
         <v>33</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" s="15">
         <v>45968.0</v>
@@ -2406,7 +2448,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>19</v>
@@ -2415,7 +2457,7 @@
         <v>33</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" s="8">
         <v>45965.0</v>
@@ -2431,7 +2473,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>19</v>
@@ -2440,7 +2482,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" s="15">
         <v>45968.0</v>
@@ -2456,16 +2498,16 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32" s="8">
         <v>45965.0</v>
@@ -2481,16 +2523,16 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E33" s="15">
         <v>45968.0</v>
@@ -2506,7 +2548,7 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>13</v>
@@ -2515,48 +2557,48 @@
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="15">
+        <v>25</v>
+      </c>
+      <c r="E34" s="8">
         <v>45967.0</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="8">
         <v>45968.0</v>
       </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
       <c r="I34" s="29"/>
       <c r="J34" s="12"/>
       <c r="K34" s="13"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8">
+        <v>25</v>
+      </c>
+      <c r="E35" s="15">
         <v>45968.0</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="15">
         <v>45968.0</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
       <c r="I35" s="29"/>
       <c r="J35" s="12"/>
       <c r="K35" s="13"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>13</v>
@@ -2565,23 +2607,23 @@
         <v>33</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="15">
+        <v>25</v>
+      </c>
+      <c r="E36" s="8">
         <v>45967.0</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="8">
         <v>45968.0</v>
       </c>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="29"/>
       <c r="J36" s="12"/>
       <c r="K36" s="13"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>19</v>
@@ -2590,16 +2632,16 @@
         <v>20</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8">
+        <v>25</v>
+      </c>
+      <c r="E37" s="15">
         <v>45968.0</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="15">
         <v>45968.0</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="29"/>
       <c r="J37" s="12"/>
       <c r="K37" s="13"/>
@@ -2679,7 +2721,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -2696,27 +2738,27 @@
         <v>4</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>13</v>
@@ -2734,26 +2776,26 @@
         <v>45944.0</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="H4" s="38"/>
       <c r="I4" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J4" s="13"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E5" s="37">
         <v>45944.0</v>
@@ -2764,19 +2806,19 @@
       <c r="G5" s="11"/>
       <c r="H5" s="38"/>
       <c r="I5" s="12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J5" s="13"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>15</v>
@@ -2788,17 +2830,17 @@
         <v>45944.0</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J6" s="13"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>13</v>
@@ -2816,23 +2858,23 @@
         <v>45944.0</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J7" s="13"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>15</v>
@@ -2844,23 +2886,23 @@
         <v>45944.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J8" s="13"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
@@ -2872,17 +2914,17 @@
         <v>45944.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J9" s="13"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>19</v>
@@ -2891,7 +2933,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="39">
         <v>45941.0</v>
@@ -2906,14 +2948,14 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="39">
         <v>45946.0</v>
@@ -2928,10 +2970,10 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>20</v>
@@ -2946,20 +2988,20 @@
         <v>45947.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H12" s="38"/>
       <c r="I12" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J12" s="13"/>
     </row>
     <row r="13">
       <c r="A13" s="42" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="44" t="s">
         <v>14</v>
@@ -2974,20 +3016,20 @@
         <v>45947.0</v>
       </c>
       <c r="G13" s="48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="49" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J13" s="50"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C14" s="51"/>
       <c r="D14" s="6" t="s">
@@ -3006,10 +3048,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>14</v>
@@ -3025,19 +3067,19 @@
       </c>
       <c r="G15" s="40"/>
       <c r="H15" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J15" s="13"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>20</v>
@@ -3052,17 +3094,17 @@
         <v>45954.0</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H16" s="38"/>
       <c r="I16" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J16" s="13"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>19</v>
@@ -3082,16 +3124,16 @@
       <c r="G17" s="11"/>
       <c r="H17" s="38"/>
       <c r="I17" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J17" s="13"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="52"/>
@@ -3108,13 +3150,13 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B19" s="53" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="55" t="s">
         <v>15</v>
@@ -3132,13 +3174,13 @@
     </row>
     <row r="20">
       <c r="A20" s="60" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="62" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D20" s="63" t="s">
         <v>15</v>
@@ -3152,21 +3194,21 @@
       <c r="G20" s="64"/>
       <c r="H20" s="65"/>
       <c r="I20" s="66" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J20" s="67" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="60" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D21" s="63" t="s">
         <v>15</v>
@@ -3178,23 +3220,23 @@
         <v>45941.0</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H21" s="65"/>
       <c r="I21" s="66" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J21" s="59"/>
     </row>
     <row r="22">
       <c r="A22" s="60" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="62" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D22" s="63" t="s">
         <v>15</v>
@@ -3206,22 +3248,22 @@
         <v>45946.0</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H22" s="69" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I22" s="66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J22" s="59"/>
     </row>
     <row r="23">
       <c r="A23" s="60" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="62" t="s">
         <v>31</v>
@@ -3236,22 +3278,22 @@
         <v>45951.0</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H23" s="65"/>
       <c r="I23" s="66" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J23" s="67" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="62" t="s">
         <v>31</v>
@@ -3266,22 +3308,22 @@
         <v>45947.0</v>
       </c>
       <c r="G24" s="68" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H24" s="65"/>
       <c r="I24" s="66" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J24" s="67" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="60" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="62" t="s">
         <v>14</v>
@@ -3298,19 +3340,19 @@
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
       <c r="I25" s="66" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J25" s="67"/>
     </row>
     <row r="26">
       <c r="A26" s="60" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D26" s="63" t="s">
         <v>15</v>
@@ -3324,16 +3366,16 @@
       <c r="G26" s="68"/>
       <c r="H26" s="65"/>
       <c r="I26" s="66" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J26" s="67"/>
     </row>
     <row r="27">
       <c r="A27" s="60" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="62" t="s">
         <v>33</v>
@@ -3350,19 +3392,19 @@
       <c r="G27" s="68"/>
       <c r="H27" s="65"/>
       <c r="I27" s="66" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J27" s="67"/>
     </row>
     <row r="28">
       <c r="A28" s="60" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" s="62" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D28" s="63" t="s">
         <v>15</v>
@@ -3376,13 +3418,13 @@
       <c r="G28" s="68"/>
       <c r="H28" s="65"/>
       <c r="I28" s="66" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J28" s="67"/>
     </row>
     <row r="29">
       <c r="A29" s="60" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B29" s="61" t="s">
         <v>13</v>
@@ -3402,13 +3444,13 @@
       <c r="G29" s="68"/>
       <c r="H29" s="65"/>
       <c r="I29" s="66" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J29" s="67"/>
     </row>
     <row r="30">
       <c r="A30" s="60" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="61" t="s">
         <v>13</v>
@@ -3426,20 +3468,20 @@
         <v>45954.0</v>
       </c>
       <c r="G30" s="68" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H30" s="65"/>
       <c r="I30" s="66" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J30" s="67"/>
     </row>
     <row r="31">
       <c r="A31" s="60" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" s="62" t="s">
         <v>14</v>
@@ -3456,13 +3498,13 @@
       <c r="G31" s="68"/>
       <c r="H31" s="65"/>
       <c r="I31" s="66" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J31" s="67"/>
     </row>
     <row r="32">
       <c r="A32" s="60" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B32" s="61" t="s">
         <v>13</v>
@@ -3471,33 +3513,33 @@
         <v>20</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E32" s="39">
         <v>45955.0</v>
       </c>
       <c r="F32" s="39"/>
       <c r="G32" s="68" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H32" s="65"/>
       <c r="I32" s="66" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J32" s="67"/>
     </row>
     <row r="33">
       <c r="A33" s="60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C33" s="62" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E33" s="39">
         <v>45954.0</v>
@@ -3508,22 +3550,22 @@
       <c r="G33" s="68"/>
       <c r="H33" s="65"/>
       <c r="I33" s="66" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J33" s="67"/>
     </row>
     <row r="34">
       <c r="A34" s="60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C34" s="62" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E34" s="39">
         <v>45955.0</v>
@@ -3534,22 +3576,22 @@
       <c r="G34" s="68"/>
       <c r="H34" s="65"/>
       <c r="I34" s="66" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J34" s="67"/>
     </row>
     <row r="35">
       <c r="A35" s="60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35" s="62" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="63" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E35" s="39">
         <v>45956.0</v>
@@ -3560,22 +3602,22 @@
       <c r="G35" s="68"/>
       <c r="H35" s="65"/>
       <c r="I35" s="66" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J35" s="67"/>
     </row>
     <row r="36">
       <c r="A36" s="60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E36" s="70">
         <v>45957.0</v>
@@ -3586,13 +3628,13 @@
       <c r="G36" s="71"/>
       <c r="H36" s="71"/>
       <c r="I36" s="72" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J36" s="73"/>
     </row>
     <row r="37">
       <c r="A37" s="74" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>19</v>
@@ -3610,17 +3652,17 @@
         <v>45958.0</v>
       </c>
       <c r="G37" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H37" s="71"/>
       <c r="I37" s="72" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J37" s="73"/>
     </row>
     <row r="38">
       <c r="A38" s="74" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>19</v>
@@ -3629,7 +3671,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E38" s="70">
         <v>45957.0</v>
@@ -3638,17 +3680,17 @@
         <v>45958.0</v>
       </c>
       <c r="G38" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H38" s="71"/>
       <c r="I38" s="72" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J38" s="73"/>
     </row>
     <row r="39">
       <c r="A39" s="74" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>19</v>
@@ -3666,23 +3708,23 @@
         <v>45958.0</v>
       </c>
       <c r="G39" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H39" s="71"/>
       <c r="I39" s="72" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J39" s="73"/>
     </row>
     <row r="40">
       <c r="A40" s="74" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>15</v>
@@ -3694,17 +3736,17 @@
         <v>45957.0</v>
       </c>
       <c r="G40" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H40" s="71"/>
       <c r="I40" s="72" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J40" s="73"/>
     </row>
     <row r="41">
       <c r="A41" s="74" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>19</v>
@@ -3722,23 +3764,23 @@
         <v>45958.0</v>
       </c>
       <c r="G41" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H41" s="71"/>
       <c r="I41" s="72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J41" s="73"/>
     </row>
     <row r="42">
       <c r="A42" s="75" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>15</v>
@@ -3750,17 +3792,17 @@
         <v>45957.0</v>
       </c>
       <c r="G42" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H42" s="71"/>
       <c r="I42" s="72" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J42" s="73"/>
     </row>
     <row r="43">
       <c r="A43" s="75" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
@@ -3778,11 +3820,11 @@
         <v>45958.0</v>
       </c>
       <c r="G43" s="72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H43" s="71"/>
       <c r="I43" s="72" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J43" s="73"/>
     </row>
@@ -3870,7 +3912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -3887,16 +3929,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>10</v>
@@ -3904,13 +3946,13 @@
     </row>
     <row r="4">
       <c r="A4" s="76" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>15</v>
@@ -3922,19 +3964,19 @@
         <v>45923.0</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H4" s="38"/>
       <c r="I4" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="76" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
@@ -3949,22 +3991,22 @@
         <v>45924.0</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H5" s="38"/>
       <c r="I5" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="76" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>15</v>
@@ -3976,16 +4018,16 @@
         <v>45924.0</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="76" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>13</v>
@@ -4003,22 +4045,22 @@
         <v>45926.0</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="76" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>15</v>
@@ -4030,22 +4072,22 @@
         <v>45926.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="76" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
@@ -4057,16 +4099,16 @@
         <v>45927.0</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="76" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>19</v>
@@ -4084,22 +4126,22 @@
         <v>45926.0</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H10" s="38"/>
       <c r="I10" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>15</v>
@@ -4111,22 +4153,22 @@
         <v>45928.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H11" s="38"/>
       <c r="I11" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>15</v>
@@ -4138,11 +4180,11 @@
         <v>45929.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H12" s="38"/>
       <c r="I12" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L12" s="79" t="str">
         <f>L9</f>
@@ -4151,13 +4193,13 @@
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>15</v>
@@ -4169,23 +4211,23 @@
         <v>45930.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H13" s="38"/>
       <c r="I13" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="38"/>
       <c r="D14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="37">
         <v>45929.0</v>
@@ -4194,19 +4236,19 @@
         <v>45930.0</v>
       </c>
       <c r="G14" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H14" s="38"/>
       <c r="I14" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="6" t="s">
@@ -4219,19 +4261,19 @@
         <v>45926.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H15" s="38"/>
       <c r="I15" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>20</v>
@@ -4246,19 +4288,19 @@
         <v>45929.0</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H16" s="38"/>
       <c r="I16" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>31</v>
@@ -4273,19 +4315,19 @@
         <v>45930.0</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="80" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B18" s="81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" s="54" t="s">
         <v>14</v>
@@ -4300,23 +4342,23 @@
         <v>45930.0</v>
       </c>
       <c r="G18" s="56" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H18" s="57"/>
       <c r="I18" s="58" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" s="37">
         <v>45930.0</v>
@@ -4325,23 +4367,23 @@
         <v>45930.0</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" s="37">
         <v>45930.0</v>
@@ -4350,22 +4392,22 @@
         <v>45901.0</v>
       </c>
       <c r="G20" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H20" s="38"/>
       <c r="I20" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>15</v>
@@ -4377,25 +4419,25 @@
         <v>45931.0</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H21" s="38"/>
       <c r="I21" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E22" s="37">
         <v>45934.0</v>
@@ -4404,19 +4446,19 @@
         <v>45934.0</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H22" s="38"/>
       <c r="I22" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>31</v>
@@ -4431,22 +4473,22 @@
         <v>45933.0</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H23" s="38"/>
       <c r="I23" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -4458,19 +4500,19 @@
         <v>45933.0</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H24" s="38"/>
       <c r="I24" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="6" t="s">
@@ -4483,14 +4525,14 @@
         <v>45932.0</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H25" s="38"/>
       <c r="I25" s="84"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>19</v>
@@ -4508,22 +4550,22 @@
         <v>45937.0</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H26" s="38"/>
       <c r="I26" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>15</v>
@@ -4535,23 +4577,23 @@
         <v>45936.0</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H27" s="38"/>
       <c r="I27" s="12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" s="37">
         <v>45934.0</v>
@@ -4560,21 +4602,21 @@
         <v>45934.0</v>
       </c>
       <c r="G28" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H28" s="38"/>
       <c r="I28" s="84"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" s="37">
         <v>45934.0</v>
@@ -4583,23 +4625,23 @@
         <v>45934.0</v>
       </c>
       <c r="G29" s="40" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H29" s="38"/>
       <c r="I29" s="84"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E30" s="37">
         <v>45935.0</v>
@@ -4608,25 +4650,25 @@
         <v>45935.0</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H30" s="38"/>
       <c r="I30" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="85" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B31" s="86" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C31" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="87" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E31" s="88">
         <v>45935.0</v>
@@ -4635,25 +4677,25 @@
         <v>45935.0</v>
       </c>
       <c r="G31" s="89" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H31" s="25"/>
       <c r="I31" s="49" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="85" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B32" s="90" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C32" s="91" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D32" s="92" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E32" s="93">
         <v>45936.0</v>
@@ -4662,16 +4704,16 @@
         <v>45936.0</v>
       </c>
       <c r="G32" s="94" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H32" s="95"/>
       <c r="I32" s="96" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>13</v>
@@ -4691,12 +4733,12 @@
       <c r="G33" s="11"/>
       <c r="H33" s="38"/>
       <c r="I33" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>13</v>
@@ -4705,7 +4747,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E34" s="37">
         <v>45940.0</v>
@@ -4714,16 +4756,16 @@
         <v>45940.0</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>13</v>
@@ -4741,22 +4783,22 @@
         <v>45940.0</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H35" s="38"/>
       <c r="I35" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>15</v>
@@ -4768,16 +4810,16 @@
         <v>45933.0</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H36" s="38"/>
       <c r="I36" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>19</v>
@@ -4786,7 +4828,7 @@
         <v>14</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E37" s="37">
         <v>45937.0</v>
@@ -4797,12 +4839,12 @@
       <c r="G37" s="11"/>
       <c r="H37" s="38"/>
       <c r="I37" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>19</v>
@@ -4818,16 +4860,16 @@
         <v>46301.0</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H38" s="38"/>
       <c r="I38" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>13</v>
@@ -4845,25 +4887,25 @@
         <v>45944.0</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="H39" s="38"/>
       <c r="I39" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E40" s="37">
         <v>45944.0</v>
@@ -4874,18 +4916,18 @@
       <c r="G40" s="11"/>
       <c r="H40" s="38"/>
       <c r="I40" s="12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>15</v>
@@ -4897,16 +4939,16 @@
         <v>45944.0</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H41" s="38"/>
       <c r="I41" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>13</v>
@@ -4924,22 +4966,22 @@
         <v>45944.0</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H42" s="38"/>
       <c r="I42" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>15</v>
@@ -4951,22 +4993,22 @@
         <v>45944.0</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H43" s="38"/>
       <c r="I43" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>15</v>
@@ -4978,25 +5020,25 @@
         <v>45944.0</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H44" s="38"/>
       <c r="I44" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="97" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B45" s="98" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C45" s="99" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D45" s="98" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E45" s="100">
         <v>45948.0</v>
@@ -5007,7 +5049,7 @@
       <c r="G45" s="101"/>
       <c r="H45" s="101"/>
       <c r="I45" s="102" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
